--- a/artfynd/A 13556-2025 artfynd.xlsx
+++ b/artfynd/A 13556-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2861691</v>
+        <v>2218627</v>
       </c>
       <c r="B2" t="n">
-        <v>96366</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjushög, SO, Öl</t>
+          <t>Tjushög, OSO, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608357.8413409636</v>
+        <v>608283</v>
       </c>
       <c r="R2" t="n">
-        <v>6296428.291537648</v>
+        <v>6296535</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-06-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Björkdunge</t>
+          <t>Fuktig blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -788,19 +773,18 @@
           <t>Åke Rühling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2307462</v>
       </c>
       <c r="B3" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608357.8413409636</v>
+        <v>608358</v>
       </c>
       <c r="R3" t="n">
-        <v>6296428.291537648</v>
+        <v>6296428</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +849,9 @@
           <t>2008-06-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +879,223 @@
           <t>Åke Rühling</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2861691</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjushög, SO, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608358</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6296428</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Björkdunge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3454634</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjushög, SO, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608389</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6296436</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Björkdunge, fuktig</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13556-2025 artfynd.xlsx
+++ b/artfynd/A 13556-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2218627</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2307462</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2861691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3454634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>